--- a/ig/main/CodeSystem-ObservationValue-supplement-fr.xlsx
+++ b/ig/main/CodeSystem-ObservationValue-supplement-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/ObservationValue-supplement-fr</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/ObservationValue-supplement-fr</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-ObservationValue-supplement-fr.xlsx
+++ b/ig/main/CodeSystem-ObservationValue-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ObservationValue|4.0.0</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ObservationValue</t>
   </si>
   <si>
     <t>Count</t>

--- a/ig/main/CodeSystem-ObservationValue-supplement-fr.xlsx
+++ b/ig/main/CodeSystem-ObservationValue-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ObservationValue</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ObservationValue|4.0.0</t>
   </si>
   <si>
     <t>Count</t>
